--- a/CPDS-AD_dataset/scenario_records/FDI_attacks/local_model_consistent/test_data_LMC_4/data_line_cabinet_meter.xlsx
+++ b/CPDS-AD_dataset/scenario_records/FDI_attacks/local_model_consistent/test_data_LMC_4/data_line_cabinet_meter.xlsx
@@ -596,7 +596,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026/6/29 23:00:00.753</t>
+          <t>2026/6/30 00:00:00.753</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -699,7 +699,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026/6/29 23:00:05.786</t>
+          <t>2026/6/30 00:00:05.786</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -802,7 +802,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026/6/29 23:00:10.753</t>
+          <t>2026/6/30 00:00:10.753</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -905,7 +905,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026/6/29 23:00:15.761</t>
+          <t>2026/6/30 00:00:15.761</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026/6/29 23:00:20.787</t>
+          <t>2026/6/30 00:00:20.787</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026/6/29 23:00:25.799</t>
+          <t>2026/6/30 00:00:25.799</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026/6/29 23:00:30.768</t>
+          <t>2026/6/30 00:00:30.768</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026/6/29 23:00:35.761</t>
+          <t>2026/6/30 00:00:35.761</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026/6/29 23:00:40.762</t>
+          <t>2026/6/30 00:00:40.762</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026/6/29 23:00:45.784</t>
+          <t>2026/6/30 00:00:45.784</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026/6/29 23:00:50.760</t>
+          <t>2026/6/30 00:00:50.760</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026/6/29 23:00:55.769</t>
+          <t>2026/6/30 00:00:55.769</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1832,7 +1832,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026/6/29 23:01:00.766</t>
+          <t>2026/6/30 00:01:00.766</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026/6/29 23:01:05.759</t>
+          <t>2026/6/30 00:01:05.759</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -2038,7 +2038,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026/6/29 23:01:10.768</t>
+          <t>2026/6/30 00:01:10.768</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026/6/29 23:01:15.793</t>
+          <t>2026/6/30 00:01:15.793</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026/6/29 23:01:20.756</t>
+          <t>2026/6/30 00:01:20.756</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -2347,7 +2347,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026/6/29 23:01:25.791</t>
+          <t>2026/6/30 00:01:25.791</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026/6/29 23:01:30.782</t>
+          <t>2026/6/30 00:01:30.782</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -2553,7 +2553,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026/6/29 23:01:35.766</t>
+          <t>2026/6/30 00:01:35.766</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026/6/29 23:01:40.799</t>
+          <t>2026/6/30 00:01:40.799</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -2759,7 +2759,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026/6/29 23:01:45.818</t>
+          <t>2026/6/30 00:01:45.818</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026/6/29 23:01:50.806</t>
+          <t>2026/6/30 00:01:50.806</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026/6/29 23:01:55.791</t>
+          <t>2026/6/30 00:01:55.791</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026/6/29 23:02:00.778</t>
+          <t>2026/6/30 00:02:00.778</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026/6/29 23:02:05.801</t>
+          <t>2026/6/30 00:02:05.801</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026/6/29 23:02:10.781</t>
+          <t>2026/6/30 00:02:10.781</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026/6/29 23:02:15.807</t>
+          <t>2026/6/30 00:02:15.807</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026/6/29 23:02:20.753</t>
+          <t>2026/6/30 00:02:20.753</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026/6/29 23:02:25.764</t>
+          <t>2026/6/30 00:02:25.764</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026/6/29 23:02:30.763</t>
+          <t>2026/6/30 00:02:30.763</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -3789,7 +3789,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026/6/29 23:02:35.805</t>
+          <t>2026/6/30 00:02:35.805</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -3892,7 +3892,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026/6/29 23:02:40.790</t>
+          <t>2026/6/30 00:02:40.790</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026/6/29 23:02:45.780</t>
+          <t>2026/6/30 00:02:45.780</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -4098,7 +4098,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026/6/29 23:02:50.800</t>
+          <t>2026/6/30 00:02:50.800</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -4201,7 +4201,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026/6/29 23:02:55.798</t>
+          <t>2026/6/30 00:02:55.798</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -4304,7 +4304,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026/6/29 23:03:00.793</t>
+          <t>2026/6/30 00:03:00.793</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -4407,7 +4407,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026/6/29 23:03:05.788</t>
+          <t>2026/6/30 00:03:05.788</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026/6/29 23:03:10.794</t>
+          <t>2026/6/30 00:03:10.794</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -4613,7 +4613,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026/6/29 23:03:15.769</t>
+          <t>2026/6/30 00:03:15.769</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026/6/29 23:03:20.803</t>
+          <t>2026/6/30 00:03:20.803</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026/6/29 23:03:25.828</t>
+          <t>2026/6/30 00:03:25.828</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -4922,7 +4922,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026/6/29 23:03:30.806</t>
+          <t>2026/6/30 00:03:30.806</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -5025,7 +5025,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026/6/29 23:03:35.827</t>
+          <t>2026/6/30 00:03:35.827</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -5128,7 +5128,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026/6/29 23:03:40.834</t>
+          <t>2026/6/30 00:03:40.834</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026/6/29 23:03:45.809</t>
+          <t>2026/6/30 00:03:45.809</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026/6/29 23:03:50.802</t>
+          <t>2026/6/30 00:03:50.802</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -5437,7 +5437,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026/6/29 23:03:55.837</t>
+          <t>2026/6/30 00:03:55.837</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -5540,7 +5540,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026/6/29 23:04:00.809</t>
+          <t>2026/6/30 00:04:00.809</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026/6/29 23:04:05.789</t>
+          <t>2026/6/30 00:04:05.789</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026/6/29 23:04:10.830</t>
+          <t>2026/6/30 00:04:10.830</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -5849,7 +5849,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026/6/29 23:04:15.827</t>
+          <t>2026/6/30 00:04:15.827</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -5952,7 +5952,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026/6/29 23:04:20.782</t>
+          <t>2026/6/30 00:04:20.782</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -6055,7 +6055,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026/6/29 23:04:25.798</t>
+          <t>2026/6/30 00:04:25.798</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026/6/29 23:04:30.827</t>
+          <t>2026/6/30 00:04:30.827</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026/6/29 23:04:35.798</t>
+          <t>2026/6/30 00:04:35.798</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -6364,7 +6364,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026/6/29 23:04:40.827</t>
+          <t>2026/6/30 00:04:40.827</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -6467,7 +6467,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026/6/29 23:04:45.816</t>
+          <t>2026/6/30 00:04:45.816</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -6570,7 +6570,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026/6/29 23:04:50.819</t>
+          <t>2026/6/30 00:04:50.819</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -6673,7 +6673,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026/6/29 23:04:55.811</t>
+          <t>2026/6/30 00:04:55.811</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -6776,7 +6776,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026/6/29 23:05:00.782</t>
+          <t>2026/6/30 00:05:00.782</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -6879,7 +6879,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026/6/29 23:05:05.799</t>
+          <t>2026/6/30 00:05:05.799</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -6982,7 +6982,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026/6/29 23:05:10.834</t>
+          <t>2026/6/30 00:05:10.834</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -7085,7 +7085,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026/6/29 23:05:15.815</t>
+          <t>2026/6/30 00:05:15.815</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -7188,7 +7188,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026/6/29 23:05:20.833</t>
+          <t>2026/6/30 00:05:20.833</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -7291,7 +7291,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026/6/29 23:05:25.834</t>
+          <t>2026/6/30 00:05:25.834</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -7394,7 +7394,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026/6/29 23:05:30.826</t>
+          <t>2026/6/30 00:05:30.826</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -7497,7 +7497,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026/6/29 23:05:35.858</t>
+          <t>2026/6/30 00:05:35.858</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -7600,7 +7600,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026/6/29 23:05:40.829</t>
+          <t>2026/6/30 00:05:40.829</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -7703,7 +7703,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026/6/29 23:05:45.797</t>
+          <t>2026/6/30 00:05:45.797</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -7806,7 +7806,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026/6/29 23:05:50.798</t>
+          <t>2026/6/30 00:05:50.798</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -7909,7 +7909,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026/6/29 23:05:55.816</t>
+          <t>2026/6/30 00:05:55.816</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -8012,7 +8012,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026/6/29 23:06:00.849</t>
+          <t>2026/6/30 00:06:00.849</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026/6/29 23:06:05.840</t>
+          <t>2026/6/30 00:06:05.840</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -8218,7 +8218,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026/6/29 23:06:10.835</t>
+          <t>2026/6/30 00:06:10.835</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -8321,7 +8321,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026/6/29 23:06:15.839</t>
+          <t>2026/6/30 00:06:15.839</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -8424,7 +8424,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026/6/29 23:06:20.833</t>
+          <t>2026/6/30 00:06:20.833</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -8527,7 +8527,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026/6/29 23:06:25.821</t>
+          <t>2026/6/30 00:06:25.821</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -8630,7 +8630,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026/6/29 23:06:30.825</t>
+          <t>2026/6/30 00:06:30.825</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -8733,7 +8733,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026/6/29 23:06:35.860</t>
+          <t>2026/6/30 00:06:35.860</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -8836,7 +8836,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026/6/29 23:06:40.836</t>
+          <t>2026/6/30 00:06:40.836</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -8939,7 +8939,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026/6/29 23:06:45.827</t>
+          <t>2026/6/30 00:06:45.827</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -9042,7 +9042,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026/6/29 23:06:50.808</t>
+          <t>2026/6/30 00:06:50.808</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -9145,7 +9145,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026/6/29 23:06:55.852</t>
+          <t>2026/6/30 00:06:55.852</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -9248,7 +9248,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026/6/29 23:07:00.837</t>
+          <t>2026/6/30 00:07:00.837</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026/6/29 23:07:05.838</t>
+          <t>2026/6/30 00:07:05.838</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -9454,7 +9454,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026/6/29 23:07:10.837</t>
+          <t>2026/6/30 00:07:10.837</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -9557,7 +9557,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026/6/29 23:07:15.829</t>
+          <t>2026/6/30 00:07:15.829</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -9660,7 +9660,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026/6/29 23:07:20.855</t>
+          <t>2026/6/30 00:07:20.855</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -9763,7 +9763,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026/6/29 23:07:25.845</t>
+          <t>2026/6/30 00:07:25.845</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -9866,7 +9866,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026/6/29 23:07:30.855</t>
+          <t>2026/6/30 00:07:30.855</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -9969,7 +9969,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026/6/29 23:07:35.814</t>
+          <t>2026/6/30 00:07:35.814</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -10072,7 +10072,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026/6/29 23:07:40.862</t>
+          <t>2026/6/30 00:07:40.862</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -10175,7 +10175,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026/6/29 23:07:45.847</t>
+          <t>2026/6/30 00:07:45.847</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -10278,7 +10278,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026/6/29 23:07:50.859</t>
+          <t>2026/6/30 00:07:50.859</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026/6/29 23:07:55.829</t>
+          <t>2026/6/30 00:07:55.829</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -10484,7 +10484,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026/6/29 23:08:00.827</t>
+          <t>2026/6/30 00:08:00.827</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -10587,7 +10587,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026/6/29 23:08:05.831</t>
+          <t>2026/6/30 00:08:05.831</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -10690,7 +10690,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026/6/29 23:08:10.830</t>
+          <t>2026/6/30 00:08:10.830</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -10793,7 +10793,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026/6/29 23:08:15.870</t>
+          <t>2026/6/30 00:08:15.870</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -10896,7 +10896,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026/6/29 23:08:20.845</t>
+          <t>2026/6/30 00:08:20.845</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -10999,7 +10999,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026/6/29 23:08:25.834</t>
+          <t>2026/6/30 00:08:25.834</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -11102,7 +11102,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026/6/29 23:08:30.870</t>
+          <t>2026/6/30 00:08:30.870</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -11205,7 +11205,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026/6/29 23:08:35.864</t>
+          <t>2026/6/30 00:08:35.864</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -11308,7 +11308,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026/6/29 23:08:40.834</t>
+          <t>2026/6/30 00:08:40.834</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -11411,7 +11411,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026/6/29 23:08:45.858</t>
+          <t>2026/6/30 00:08:45.858</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -11514,7 +11514,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026/6/29 23:08:50.842</t>
+          <t>2026/6/30 00:08:50.842</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -11617,7 +11617,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026/6/29 23:08:55.861</t>
+          <t>2026/6/30 00:08:55.861</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -11720,7 +11720,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026/6/29 23:09:00.840</t>
+          <t>2026/6/30 00:09:00.840</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -11823,7 +11823,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026/6/29 23:09:05.876</t>
+          <t>2026/6/30 00:09:05.876</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -11926,7 +11926,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026/6/29 23:09:10.836</t>
+          <t>2026/6/30 00:09:10.836</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -12029,7 +12029,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026/6/29 23:09:15.851</t>
+          <t>2026/6/30 00:09:15.851</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -12132,7 +12132,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026/6/29 23:09:20.870</t>
+          <t>2026/6/30 00:09:20.870</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -12235,7 +12235,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026/6/29 23:09:25.893</t>
+          <t>2026/6/30 00:09:25.893</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026/6/29 23:09:30.873</t>
+          <t>2026/6/30 00:09:30.873</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -12441,7 +12441,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026/6/29 23:09:35.856</t>
+          <t>2026/6/30 00:09:35.856</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -12544,7 +12544,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026/6/29 23:09:40.859</t>
+          <t>2026/6/30 00:09:40.859</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -12647,7 +12647,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026/6/29 23:09:45.882</t>
+          <t>2026/6/30 00:09:45.882</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -12750,7 +12750,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026/6/29 23:09:50.852</t>
+          <t>2026/6/30 00:09:50.852</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -12853,7 +12853,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026/6/29 23:09:55.865</t>
+          <t>2026/6/30 00:09:55.865</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -12956,7 +12956,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026/6/29 23:10:00.838</t>
+          <t>2026/6/30 00:10:00.838</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -13059,7 +13059,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026/6/29 23:10:05.841</t>
+          <t>2026/6/30 00:10:05.841</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -13162,7 +13162,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026/6/29 23:10:10.866</t>
+          <t>2026/6/30 00:10:10.866</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -13265,7 +13265,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026/6/29 23:10:15.860</t>
+          <t>2026/6/30 00:10:15.860</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -13368,7 +13368,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026/6/29 23:10:20.883</t>
+          <t>2026/6/30 00:10:20.883</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -13471,7 +13471,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026/6/29 23:10:25.848</t>
+          <t>2026/6/30 00:10:25.848</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -13574,7 +13574,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026/6/29 23:10:30.862</t>
+          <t>2026/6/30 00:10:30.862</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -13677,7 +13677,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026/6/29 23:10:35.864</t>
+          <t>2026/6/30 00:10:35.864</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -13780,7 +13780,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026/6/29 23:10:40.855</t>
+          <t>2026/6/30 00:10:40.855</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -13883,7 +13883,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026/6/29 23:10:45.897</t>
+          <t>2026/6/30 00:10:45.897</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -13986,7 +13986,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026/6/29 23:10:50.848</t>
+          <t>2026/6/30 00:10:50.848</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -14089,7 +14089,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026/6/29 23:10:55.871</t>
+          <t>2026/6/30 00:10:55.871</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -14192,7 +14192,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026/6/29 23:11:00.887</t>
+          <t>2026/6/30 00:11:00.887</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -14295,7 +14295,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026/6/29 23:11:05.875</t>
+          <t>2026/6/30 00:11:05.875</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -14398,7 +14398,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026/6/29 23:11:10.908</t>
+          <t>2026/6/30 00:11:10.908</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -14501,7 +14501,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026/6/29 23:11:15.864</t>
+          <t>2026/6/30 00:11:15.864</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -14604,7 +14604,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026/6/29 23:11:20.892</t>
+          <t>2026/6/30 00:11:20.892</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -14707,7 +14707,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026/6/29 23:11:25.904</t>
+          <t>2026/6/30 00:11:25.904</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -14810,7 +14810,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026/6/29 23:11:30.873</t>
+          <t>2026/6/30 00:11:30.873</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -14913,7 +14913,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026/6/29 23:11:35.903</t>
+          <t>2026/6/30 00:11:35.903</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -15016,7 +15016,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026/6/29 23:11:40.877</t>
+          <t>2026/6/30 00:11:40.877</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -15119,7 +15119,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026/6/29 23:11:45.902</t>
+          <t>2026/6/30 00:11:45.902</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -15222,7 +15222,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026/6/29 23:11:50.885</t>
+          <t>2026/6/30 00:11:50.885</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -15325,7 +15325,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026/6/29 23:11:55.905</t>
+          <t>2026/6/30 00:11:55.905</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -15428,7 +15428,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026/6/29 23:12:00.873</t>
+          <t>2026/6/30 00:12:00.873</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -15531,7 +15531,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026/6/29 23:12:05.914</t>
+          <t>2026/6/30 00:12:05.914</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -15634,7 +15634,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026/6/29 23:12:10.889</t>
+          <t>2026/6/30 00:12:10.889</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -15737,7 +15737,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026/6/29 23:12:15.915</t>
+          <t>2026/6/30 00:12:15.915</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -15840,7 +15840,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026/6/29 23:12:20.882</t>
+          <t>2026/6/30 00:12:20.882</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -15943,7 +15943,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026/6/29 23:12:25.920</t>
+          <t>2026/6/30 00:12:25.920</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -16046,7 +16046,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026/6/29 23:12:30.901</t>
+          <t>2026/6/30 00:12:30.901</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -16149,7 +16149,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026/6/29 23:12:35.860</t>
+          <t>2026/6/30 00:12:35.860</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -16252,7 +16252,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026/6/29 23:12:40.916</t>
+          <t>2026/6/30 00:12:40.916</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -16355,7 +16355,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026/6/29 23:12:45.887</t>
+          <t>2026/6/30 00:12:45.887</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -16458,7 +16458,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026/6/29 23:12:50.900</t>
+          <t>2026/6/30 00:12:50.900</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -16561,7 +16561,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026/6/29 23:12:55.904</t>
+          <t>2026/6/30 00:12:55.904</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -16664,7 +16664,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026/6/29 23:13:00.894</t>
+          <t>2026/6/30 00:13:00.894</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -16767,7 +16767,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026/6/29 23:13:05.901</t>
+          <t>2026/6/30 00:13:05.901</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -16870,7 +16870,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026/6/29 23:13:10.885</t>
+          <t>2026/6/30 00:13:10.885</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -16973,7 +16973,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026/6/29 23:13:15.892</t>
+          <t>2026/6/30 00:13:15.892</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -17076,7 +17076,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026/6/29 23:13:20.894</t>
+          <t>2026/6/30 00:13:20.894</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -17179,7 +17179,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026/6/29 23:13:25.891</t>
+          <t>2026/6/30 00:13:25.891</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -17282,7 +17282,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026/6/29 23:13:30.895</t>
+          <t>2026/6/30 00:13:30.895</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -17385,7 +17385,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026/6/29 23:13:35.907</t>
+          <t>2026/6/30 00:13:35.907</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -17488,7 +17488,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026/6/29 23:13:40.934</t>
+          <t>2026/6/30 00:13:40.934</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -17591,7 +17591,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026/6/29 23:13:45.898</t>
+          <t>2026/6/30 00:13:45.898</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -17694,7 +17694,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026/6/29 23:13:50.892</t>
+          <t>2026/6/30 00:13:50.892</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -17797,7 +17797,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026/6/29 23:13:55.914</t>
+          <t>2026/6/30 00:13:55.914</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -17900,7 +17900,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026/6/29 23:14:00.931</t>
+          <t>2026/6/30 00:14:00.931</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -18003,7 +18003,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026/6/29 23:14:05.888</t>
+          <t>2026/6/30 00:14:05.888</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -18106,7 +18106,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026/6/29 23:14:10.912</t>
+          <t>2026/6/30 00:14:10.912</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -18209,7 +18209,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026/6/29 23:14:15.941</t>
+          <t>2026/6/30 00:14:15.941</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -18312,7 +18312,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026/6/29 23:14:20.898</t>
+          <t>2026/6/30 00:14:20.898</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -18415,7 +18415,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026/6/29 23:14:25.887</t>
+          <t>2026/6/30 00:14:25.887</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -18518,7 +18518,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026/6/29 23:14:30.916</t>
+          <t>2026/6/30 00:14:30.916</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -18621,7 +18621,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026/6/29 23:14:35.910</t>
+          <t>2026/6/30 00:14:35.910</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -18724,7 +18724,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026/6/29 23:14:40.911</t>
+          <t>2026/6/30 00:14:40.911</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -18827,7 +18827,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026/6/29 23:14:45.911</t>
+          <t>2026/6/30 00:14:45.911</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -18930,7 +18930,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026/6/29 23:14:50.915</t>
+          <t>2026/6/30 00:14:50.915</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -19033,7 +19033,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026/6/29 23:14:55.933</t>
+          <t>2026/6/30 00:14:55.933</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -19136,7 +19136,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026/6/29 23:15:00.904</t>
+          <t>2026/6/30 00:15:00.904</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -19239,7 +19239,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026/6/29 23:15:05.940</t>
+          <t>2026/6/30 00:15:05.940</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -19342,7 +19342,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026/6/29 23:15:10.942</t>
+          <t>2026/6/30 00:15:10.942</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -19445,7 +19445,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026/6/29 23:15:15.922</t>
+          <t>2026/6/30 00:15:15.922</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -19548,7 +19548,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026/6/29 23:15:20.909</t>
+          <t>2026/6/30 00:15:20.909</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -19651,7 +19651,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026/6/29 23:15:25.900</t>
+          <t>2026/6/30 00:15:25.900</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -19754,7 +19754,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026/6/29 23:15:30.918</t>
+          <t>2026/6/30 00:15:30.918</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -19857,7 +19857,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026/6/29 23:15:35.904</t>
+          <t>2026/6/30 00:15:35.904</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -19960,7 +19960,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026/6/29 23:15:40.938</t>
+          <t>2026/6/30 00:15:40.938</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -20063,7 +20063,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026/6/29 23:15:45.904</t>
+          <t>2026/6/30 00:15:45.904</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -20166,7 +20166,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026/6/29 23:15:50.955</t>
+          <t>2026/6/30 00:15:50.955</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -20269,7 +20269,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026/6/29 23:15:55.934</t>
+          <t>2026/6/30 00:15:55.934</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -20372,7 +20372,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026/6/29 23:16:00.936</t>
+          <t>2026/6/30 00:16:00.936</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -20475,7 +20475,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026/6/29 23:16:05.950</t>
+          <t>2026/6/30 00:16:05.950</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -20578,7 +20578,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026/6/29 23:16:10.901</t>
+          <t>2026/6/30 00:16:10.901</t>
         </is>
       </c>
       <c r="C196" t="n">
@@ -20681,7 +20681,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026/6/29 23:16:15.909</t>
+          <t>2026/6/30 00:16:15.909</t>
         </is>
       </c>
       <c r="C197" t="n">
@@ -20784,7 +20784,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026/6/29 23:16:20.917</t>
+          <t>2026/6/30 00:16:20.917</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -20887,7 +20887,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026/6/29 23:16:25.927</t>
+          <t>2026/6/30 00:16:25.927</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -20990,7 +20990,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026/6/29 23:16:30.927</t>
+          <t>2026/6/30 00:16:30.927</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -21093,7 +21093,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026/6/29 23:16:35.948</t>
+          <t>2026/6/30 00:16:35.948</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -21196,7 +21196,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026/6/29 23:16:40.910</t>
+          <t>2026/6/30 00:16:40.910</t>
         </is>
       </c>
       <c r="C202" t="n">
@@ -21299,7 +21299,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026/6/29 23:16:45.947</t>
+          <t>2026/6/30 00:16:45.947</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -21402,7 +21402,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026/6/29 23:16:50.924</t>
+          <t>2026/6/30 00:16:50.924</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -21505,7 +21505,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026/6/29 23:16:55.943</t>
+          <t>2026/6/30 00:16:55.943</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -21608,7 +21608,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026/6/29 23:17:00.966</t>
+          <t>2026/6/30 00:17:00.966</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -21711,7 +21711,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026/6/29 23:17:05.942</t>
+          <t>2026/6/30 00:17:05.942</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -21814,7 +21814,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026/6/29 23:17:10.948</t>
+          <t>2026/6/30 00:17:10.948</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -21917,7 +21917,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026/6/29 23:17:15.951</t>
+          <t>2026/6/30 00:17:15.951</t>
         </is>
       </c>
       <c r="C209" t="n">
@@ -22020,7 +22020,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026/6/29 23:17:20.944</t>
+          <t>2026/6/30 00:17:20.944</t>
         </is>
       </c>
       <c r="C210" t="n">
@@ -22123,7 +22123,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026/6/29 23:17:25.938</t>
+          <t>2026/6/30 00:17:25.938</t>
         </is>
       </c>
       <c r="C211" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026/6/29 23:17:30.974</t>
+          <t>2026/6/30 00:17:30.974</t>
         </is>
       </c>
       <c r="C212" t="n">
@@ -22329,7 +22329,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026/6/29 23:17:35.934</t>
+          <t>2026/6/30 00:17:35.934</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -22432,7 +22432,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026/6/29 23:17:40.933</t>
+          <t>2026/6/30 00:17:40.933</t>
         </is>
       </c>
       <c r="C214" t="n">
@@ -22535,7 +22535,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026/6/29 23:17:45.967</t>
+          <t>2026/6/30 00:17:45.967</t>
         </is>
       </c>
       <c r="C215" t="n">
@@ -22638,7 +22638,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026/6/29 23:17:50.927</t>
+          <t>2026/6/30 00:17:50.927</t>
         </is>
       </c>
       <c r="C216" t="n">
@@ -22741,7 +22741,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026/6/29 23:17:55.957</t>
+          <t>2026/6/30 00:17:55.957</t>
         </is>
       </c>
       <c r="C217" t="n">
@@ -22844,7 +22844,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026/6/29 23:18:00.972</t>
+          <t>2026/6/30 00:18:00.972</t>
         </is>
       </c>
       <c r="C218" t="n">
@@ -22947,7 +22947,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026/6/29 23:18:05.952</t>
+          <t>2026/6/30 00:18:05.952</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -23050,7 +23050,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2026/6/29 23:18:10.925</t>
+          <t>2026/6/30 00:18:10.925</t>
         </is>
       </c>
       <c r="C220" t="n">
@@ -23153,7 +23153,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026/6/29 23:18:15.944</t>
+          <t>2026/6/30 00:18:15.944</t>
         </is>
       </c>
       <c r="C221" t="n">
@@ -23256,7 +23256,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026/6/29 23:18:20.967</t>
+          <t>2026/6/30 00:18:20.967</t>
         </is>
       </c>
       <c r="C222" t="n">
@@ -23359,7 +23359,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026/6/29 23:18:25.935</t>
+          <t>2026/6/30 00:18:25.935</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -23462,7 +23462,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026/6/29 23:18:30.924</t>
+          <t>2026/6/30 00:18:30.924</t>
         </is>
       </c>
       <c r="C224" t="n">
@@ -23565,7 +23565,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026/6/29 23:18:35.950</t>
+          <t>2026/6/30 00:18:35.950</t>
         </is>
       </c>
       <c r="C225" t="n">
@@ -23668,7 +23668,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026/6/29 23:18:40.988</t>
+          <t>2026/6/30 00:18:40.988</t>
         </is>
       </c>
       <c r="C226" t="n">
@@ -23771,7 +23771,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2026/6/29 23:18:45.931</t>
+          <t>2026/6/30 00:18:45.931</t>
         </is>
       </c>
       <c r="C227" t="n">
@@ -23874,7 +23874,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2026/6/29 23:18:50.970</t>
+          <t>2026/6/30 00:18:50.970</t>
         </is>
       </c>
       <c r="C228" t="n">
@@ -23977,7 +23977,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2026/6/29 23:18:55.967</t>
+          <t>2026/6/30 00:18:55.967</t>
         </is>
       </c>
       <c r="C229" t="n">
@@ -24080,7 +24080,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2026/6/29 23:19:00.977</t>
+          <t>2026/6/30 00:19:00.977</t>
         </is>
       </c>
       <c r="C230" t="n">
@@ -24183,7 +24183,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2026/6/29 23:19:05.969</t>
+          <t>2026/6/30 00:19:05.969</t>
         </is>
       </c>
       <c r="C231" t="n">
@@ -24286,7 +24286,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2026/6/29 23:19:10.970</t>
+          <t>2026/6/30 00:19:10.970</t>
         </is>
       </c>
       <c r="C232" t="n">
@@ -24389,7 +24389,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2026/6/29 23:19:15.969</t>
+          <t>2026/6/30 00:19:15.969</t>
         </is>
       </c>
       <c r="C233" t="n">
@@ -24492,7 +24492,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2026/6/29 23:19:20.943</t>
+          <t>2026/6/30 00:19:20.943</t>
         </is>
       </c>
       <c r="C234" t="n">
@@ -24595,7 +24595,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2026/6/29 23:19:25.984</t>
+          <t>2026/6/30 00:19:25.984</t>
         </is>
       </c>
       <c r="C235" t="n">
@@ -24698,7 +24698,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>2026/6/29 23:19:30.972</t>
+          <t>2026/6/30 00:19:30.972</t>
         </is>
       </c>
       <c r="C236" t="n">
@@ -24801,7 +24801,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>2026/6/29 23:19:35.950</t>
+          <t>2026/6/30 00:19:35.950</t>
         </is>
       </c>
       <c r="C237" t="n">
@@ -24904,7 +24904,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>2026/6/29 23:19:40.962</t>
+          <t>2026/6/30 00:19:40.962</t>
         </is>
       </c>
       <c r="C238" t="n">
@@ -25007,7 +25007,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>2026/6/29 23:19:45.958</t>
+          <t>2026/6/30 00:19:45.958</t>
         </is>
       </c>
       <c r="C239" t="n">
@@ -25110,7 +25110,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>2026/6/29 23:19:50.987</t>
+          <t>2026/6/30 00:19:50.987</t>
         </is>
       </c>
       <c r="C240" t="n">
@@ -25213,7 +25213,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>2026/6/29 23:19:55.960</t>
+          <t>2026/6/30 00:19:55.960</t>
         </is>
       </c>
       <c r="C241" t="n">
@@ -25316,7 +25316,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>2026/6/29 23:20:00.946</t>
+          <t>2026/6/30 00:20:00.946</t>
         </is>
       </c>
       <c r="C242" t="n">
@@ -25419,7 +25419,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>2026/6/29 23:20:05.943</t>
+          <t>2026/6/30 00:20:05.943</t>
         </is>
       </c>
       <c r="C243" t="n">
@@ -25522,7 +25522,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>2026/6/29 23:20:11.000</t>
+          <t>2026/6/30 00:20:11.000</t>
         </is>
       </c>
       <c r="C244" t="n">
@@ -25625,7 +25625,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>2026/6/29 23:20:15.963</t>
+          <t>2026/6/30 00:20:15.963</t>
         </is>
       </c>
       <c r="C245" t="n">
@@ -25728,7 +25728,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>2026/6/29 23:20:20.987</t>
+          <t>2026/6/30 00:20:20.987</t>
         </is>
       </c>
       <c r="C246" t="n">
@@ -25831,7 +25831,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>2026/6/29 23:20:25.979</t>
+          <t>2026/6/30 00:20:25.979</t>
         </is>
       </c>
       <c r="C247" t="n">
@@ -25934,7 +25934,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>2026/6/29 23:20:30.993</t>
+          <t>2026/6/30 00:20:30.993</t>
         </is>
       </c>
       <c r="C248" t="n">
@@ -26037,7 +26037,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>2026/6/29 23:20:35.957</t>
+          <t>2026/6/30 00:20:35.957</t>
         </is>
       </c>
       <c r="C249" t="n">
@@ -26140,7 +26140,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>2026/6/29 23:20:40.988</t>
+          <t>2026/6/30 00:20:40.988</t>
         </is>
       </c>
       <c r="C250" t="n">
@@ -26243,7 +26243,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>2026/6/29 23:20:45.991</t>
+          <t>2026/6/30 00:20:45.991</t>
         </is>
       </c>
       <c r="C251" t="n">
@@ -26346,7 +26346,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>2026/6/29 23:20:50.971</t>
+          <t>2026/6/30 00:20:50.971</t>
         </is>
       </c>
       <c r="C252" t="n">
@@ -26449,7 +26449,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>2026/6/29 23:20:55.984</t>
+          <t>2026/6/30 00:20:55.984</t>
         </is>
       </c>
       <c r="C253" t="n">
@@ -26552,7 +26552,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>2026/6/29 23:21:00.988</t>
+          <t>2026/6/30 00:21:00.988</t>
         </is>
       </c>
       <c r="C254" t="n">
@@ -26655,7 +26655,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>2026/6/29 23:21:05.974</t>
+          <t>2026/6/30 00:21:05.974</t>
         </is>
       </c>
       <c r="C255" t="n">
@@ -26758,7 +26758,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>2026/6/29 23:21:11.009</t>
+          <t>2026/6/30 00:21:11.009</t>
         </is>
       </c>
       <c r="C256" t="n">
@@ -26861,7 +26861,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>2026/6/29 23:21:16.001</t>
+          <t>2026/6/30 00:21:16.001</t>
         </is>
       </c>
       <c r="C257" t="n">
@@ -26964,7 +26964,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>2026/6/29 23:21:20.967</t>
+          <t>2026/6/30 00:21:20.967</t>
         </is>
       </c>
       <c r="C258" t="n">
@@ -27067,7 +27067,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>2026/6/29 23:21:25.976</t>
+          <t>2026/6/30 00:21:25.976</t>
         </is>
       </c>
       <c r="C259" t="n">
@@ -27170,7 +27170,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>2026/6/29 23:21:30.973</t>
+          <t>2026/6/30 00:21:30.973</t>
         </is>
       </c>
       <c r="C260" t="n">
@@ -27273,7 +27273,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>2026/6/29 23:21:35.988</t>
+          <t>2026/6/30 00:21:35.988</t>
         </is>
       </c>
       <c r="C261" t="n">
@@ -27376,7 +27376,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>2026/6/29 23:21:41.006</t>
+          <t>2026/6/30 00:21:41.006</t>
         </is>
       </c>
       <c r="C262" t="n">
@@ -27479,7 +27479,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>2026/6/29 23:21:45.994</t>
+          <t>2026/6/30 00:21:45.994</t>
         </is>
       </c>
       <c r="C263" t="n">
@@ -27582,7 +27582,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>2026/6/29 23:21:51.022</t>
+          <t>2026/6/30 00:21:51.022</t>
         </is>
       </c>
       <c r="C264" t="n">
@@ -27685,7 +27685,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>2026/6/29 23:21:56.023</t>
+          <t>2026/6/30 00:21:56.023</t>
         </is>
       </c>
       <c r="C265" t="n">
@@ -27788,7 +27788,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>2026/6/29 23:22:01.002</t>
+          <t>2026/6/30 00:22:01.002</t>
         </is>
       </c>
       <c r="C266" t="n">
@@ -27891,7 +27891,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>2026/6/29 23:22:06.007</t>
+          <t>2026/6/30 00:22:06.007</t>
         </is>
       </c>
       <c r="C267" t="n">
@@ -27994,7 +27994,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>2026/6/29 23:22:10.994</t>
+          <t>2026/6/30 00:22:10.994</t>
         </is>
       </c>
       <c r="C268" t="n">
@@ -28097,7 +28097,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>2026/6/29 23:22:15.957</t>
+          <t>2026/6/30 00:22:15.957</t>
         </is>
       </c>
       <c r="C269" t="n">
@@ -28200,7 +28200,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>2026/6/29 23:22:20.973</t>
+          <t>2026/6/30 00:22:20.973</t>
         </is>
       </c>
       <c r="C270" t="n">
@@ -28303,7 +28303,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>2026/6/29 23:22:25.965</t>
+          <t>2026/6/30 00:22:25.965</t>
         </is>
       </c>
       <c r="C271" t="n">
@@ -28406,7 +28406,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>2026/6/29 23:22:30.986</t>
+          <t>2026/6/30 00:22:30.986</t>
         </is>
       </c>
       <c r="C272" t="n">
@@ -28509,7 +28509,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>2026/6/29 23:22:36.015</t>
+          <t>2026/6/30 00:22:36.015</t>
         </is>
       </c>
       <c r="C273" t="n">
@@ -28612,7 +28612,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>2026/6/29 23:22:41.024</t>
+          <t>2026/6/30 00:22:41.024</t>
         </is>
       </c>
       <c r="C274" t="n">
@@ -28715,7 +28715,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>2026/6/29 23:22:46.014</t>
+          <t>2026/6/30 00:22:46.014</t>
         </is>
       </c>
       <c r="C275" t="n">
@@ -28818,7 +28818,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>2026/6/29 23:22:51.011</t>
+          <t>2026/6/30 00:22:51.011</t>
         </is>
       </c>
       <c r="C276" t="n">
@@ -28921,7 +28921,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>2026/6/29 23:22:55.994</t>
+          <t>2026/6/30 00:22:55.994</t>
         </is>
       </c>
       <c r="C277" t="n">
@@ -29024,7 +29024,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>2026/6/29 23:23:01.011</t>
+          <t>2026/6/30 00:23:01.011</t>
         </is>
       </c>
       <c r="C278" t="n">
@@ -29127,7 +29127,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>2026/6/29 23:23:05.981</t>
+          <t>2026/6/30 00:23:05.981</t>
         </is>
       </c>
       <c r="C279" t="n">
@@ -29230,7 +29230,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>2026/6/29 23:23:11.021</t>
+          <t>2026/6/30 00:23:11.021</t>
         </is>
       </c>
       <c r="C280" t="n">
@@ -29333,7 +29333,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>2026/6/29 23:23:16.006</t>
+          <t>2026/6/30 00:23:16.006</t>
         </is>
       </c>
       <c r="C281" t="n">
@@ -29436,7 +29436,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>2026/6/29 23:23:21.022</t>
+          <t>2026/6/30 00:23:21.022</t>
         </is>
       </c>
       <c r="C282" t="n">
@@ -29539,7 +29539,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>2026/6/29 23:23:25.993</t>
+          <t>2026/6/30 00:23:25.993</t>
         </is>
       </c>
       <c r="C283" t="n">
@@ -29642,7 +29642,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>2026/6/29 23:23:30.992</t>
+          <t>2026/6/30 00:23:30.992</t>
         </is>
       </c>
       <c r="C284" t="n">
@@ -29745,7 +29745,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>2026/6/29 23:23:36.013</t>
+          <t>2026/6/30 00:23:36.013</t>
         </is>
       </c>
       <c r="C285" t="n">
@@ -29848,7 +29848,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>2026/6/29 23:23:41.007</t>
+          <t>2026/6/30 00:23:41.007</t>
         </is>
       </c>
       <c r="C286" t="n">
@@ -29951,7 +29951,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>2026/6/29 23:23:45.978</t>
+          <t>2026/6/30 00:23:45.978</t>
         </is>
       </c>
       <c r="C287" t="n">
@@ -30054,7 +30054,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>2026/6/29 23:23:50.998</t>
+          <t>2026/6/30 00:23:50.998</t>
         </is>
       </c>
       <c r="C288" t="n">
@@ -30157,7 +30157,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>2026/6/29 23:23:56.015</t>
+          <t>2026/6/30 00:23:56.015</t>
         </is>
       </c>
       <c r="C289" t="n">
@@ -30260,7 +30260,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>2026/6/29 23:24:00.999</t>
+          <t>2026/6/30 00:24:00.999</t>
         </is>
       </c>
       <c r="C290" t="n">
@@ -30363,7 +30363,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>2026/6/29 23:24:06.030</t>
+          <t>2026/6/30 00:24:06.030</t>
         </is>
       </c>
       <c r="C291" t="n">
@@ -30466,7 +30466,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>2026/6/29 23:24:10.986</t>
+          <t>2026/6/30 00:24:10.986</t>
         </is>
       </c>
       <c r="C292" t="n">
@@ -30569,7 +30569,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>2026/6/29 23:24:16.022</t>
+          <t>2026/6/30 00:24:16.022</t>
         </is>
       </c>
       <c r="C293" t="n">
@@ -30672,7 +30672,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>2026/6/29 23:24:21.010</t>
+          <t>2026/6/30 00:24:21.010</t>
         </is>
       </c>
       <c r="C294" t="n">
@@ -30775,7 +30775,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>2026/6/29 23:24:26.037</t>
+          <t>2026/6/30 00:24:26.037</t>
         </is>
       </c>
       <c r="C295" t="n">
@@ -30878,7 +30878,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>2026/6/29 23:24:30.999</t>
+          <t>2026/6/30 00:24:30.999</t>
         </is>
       </c>
       <c r="C296" t="n">
@@ -30981,7 +30981,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>2026/6/29 23:24:36.030</t>
+          <t>2026/6/30 00:24:36.030</t>
         </is>
       </c>
       <c r="C297" t="n">
@@ -31084,7 +31084,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>2026/6/29 23:24:41.027</t>
+          <t>2026/6/30 00:24:41.027</t>
         </is>
       </c>
       <c r="C298" t="n">
@@ -31187,7 +31187,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>2026/6/29 23:24:46.014</t>
+          <t>2026/6/30 00:24:46.014</t>
         </is>
       </c>
       <c r="C299" t="n">
@@ -31290,7 +31290,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>2026/6/29 23:24:51.015</t>
+          <t>2026/6/30 00:24:51.015</t>
         </is>
       </c>
       <c r="C300" t="n">
@@ -31393,7 +31393,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>2026/6/29 23:24:56.002</t>
+          <t>2026/6/30 00:24:56.002</t>
         </is>
       </c>
       <c r="C301" t="n">
@@ -31496,7 +31496,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>2026/6/29 23:25:01.032</t>
+          <t>2026/6/30 00:25:01.032</t>
         </is>
       </c>
       <c r="C302" t="n">
@@ -31599,7 +31599,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>2026/6/29 23:25:06.035</t>
+          <t>2026/6/30 00:25:06.035</t>
         </is>
       </c>
       <c r="C303" t="n">
@@ -31702,7 +31702,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>2026/6/29 23:25:11.037</t>
+          <t>2026/6/30 00:25:11.037</t>
         </is>
       </c>
       <c r="C304" t="n">
@@ -31805,7 +31805,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>2026/6/29 23:25:16.021</t>
+          <t>2026/6/30 00:25:16.021</t>
         </is>
       </c>
       <c r="C305" t="n">
@@ -31908,7 +31908,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>2026/6/29 23:25:21.000</t>
+          <t>2026/6/30 00:25:21.000</t>
         </is>
       </c>
       <c r="C306" t="n">
@@ -32011,7 +32011,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>2026/6/29 23:25:26.020</t>
+          <t>2026/6/30 00:25:26.020</t>
         </is>
       </c>
       <c r="C307" t="n">
@@ -32114,7 +32114,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>2026/6/29 23:25:31.041</t>
+          <t>2026/6/30 00:25:31.041</t>
         </is>
       </c>
       <c r="C308" t="n">
@@ -32217,7 +32217,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>2026/6/29 23:25:36.017</t>
+          <t>2026/6/30 00:25:36.017</t>
         </is>
       </c>
       <c r="C309" t="n">
@@ -32320,7 +32320,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>2026/6/29 23:25:41.048</t>
+          <t>2026/6/30 00:25:41.048</t>
         </is>
       </c>
       <c r="C310" t="n">
@@ -32423,7 +32423,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>2026/6/29 23:25:45.993</t>
+          <t>2026/6/30 00:25:45.993</t>
         </is>
       </c>
       <c r="C311" t="n">
@@ -32526,7 +32526,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>2026/6/29 23:25:51.036</t>
+          <t>2026/6/30 00:25:51.036</t>
         </is>
       </c>
       <c r="C312" t="n">
@@ -32629,7 +32629,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>2026/6/29 23:25:56.010</t>
+          <t>2026/6/30 00:25:56.010</t>
         </is>
       </c>
       <c r="C313" t="n">
@@ -32732,7 +32732,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>2026/6/29 23:26:01.008</t>
+          <t>2026/6/30 00:26:01.008</t>
         </is>
       </c>
       <c r="C314" t="n">
@@ -32835,7 +32835,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>2026/6/29 23:26:06.005</t>
+          <t>2026/6/30 00:26:06.005</t>
         </is>
       </c>
       <c r="C315" t="n">
@@ -32938,7 +32938,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>2026/6/29 23:26:11.040</t>
+          <t>2026/6/30 00:26:11.040</t>
         </is>
       </c>
       <c r="C316" t="n">
@@ -33041,7 +33041,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>2026/6/29 23:26:16.025</t>
+          <t>2026/6/30 00:26:16.025</t>
         </is>
       </c>
       <c r="C317" t="n">
@@ -33144,7 +33144,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>2026/6/29 23:26:21.025</t>
+          <t>2026/6/30 00:26:21.025</t>
         </is>
       </c>
       <c r="C318" t="n">
@@ -33247,7 +33247,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>2026/6/29 23:26:26.008</t>
+          <t>2026/6/30 00:26:26.008</t>
         </is>
       </c>
       <c r="C319" t="n">
@@ -33350,7 +33350,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>2026/6/29 23:26:31.022</t>
+          <t>2026/6/30 00:26:31.022</t>
         </is>
       </c>
       <c r="C320" t="n">
@@ -33453,7 +33453,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>2026/6/29 23:26:36.004</t>
+          <t>2026/6/30 00:26:36.004</t>
         </is>
       </c>
       <c r="C321" t="n">
@@ -33556,7 +33556,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>2026/6/29 23:26:41.045</t>
+          <t>2026/6/30 00:26:41.045</t>
         </is>
       </c>
       <c r="C322" t="n">
@@ -33659,7 +33659,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>2026/6/29 23:26:46.015</t>
+          <t>2026/6/30 00:26:46.015</t>
         </is>
       </c>
       <c r="C323" t="n">
@@ -33762,7 +33762,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>2026/6/29 23:26:51.018</t>
+          <t>2026/6/30 00:26:51.018</t>
         </is>
       </c>
       <c r="C324" t="n">
@@ -33865,7 +33865,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>2026/6/29 23:26:56.015</t>
+          <t>2026/6/30 00:26:56.015</t>
         </is>
       </c>
       <c r="C325" t="n">
@@ -33968,7 +33968,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>2026/6/29 23:27:01.056</t>
+          <t>2026/6/30 00:27:01.056</t>
         </is>
       </c>
       <c r="C326" t="n">
@@ -34071,7 +34071,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>2026/6/29 23:27:06.037</t>
+          <t>2026/6/30 00:27:06.037</t>
         </is>
       </c>
       <c r="C327" t="n">
@@ -34174,7 +34174,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>2026/6/29 23:27:11.035</t>
+          <t>2026/6/30 00:27:11.035</t>
         </is>
       </c>
       <c r="C328" t="n">
@@ -34277,7 +34277,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>2026/6/29 23:27:16.039</t>
+          <t>2026/6/30 00:27:16.039</t>
         </is>
       </c>
       <c r="C329" t="n">
@@ -34380,7 +34380,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>2026/6/29 23:27:21.045</t>
+          <t>2026/6/30 00:27:21.045</t>
         </is>
       </c>
       <c r="C330" t="n">
@@ -34483,7 +34483,7 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>2026/6/29 23:27:26.015</t>
+          <t>2026/6/30 00:27:26.015</t>
         </is>
       </c>
       <c r="C331" t="n">
@@ -34586,7 +34586,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>2026/6/29 23:27:31.044</t>
+          <t>2026/6/30 00:27:31.044</t>
         </is>
       </c>
       <c r="C332" t="n">
@@ -34689,7 +34689,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>2026/6/29 23:27:36.016</t>
+          <t>2026/6/30 00:27:36.016</t>
         </is>
       </c>
       <c r="C333" t="n">
@@ -34792,7 +34792,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>2026/6/29 23:27:41.020</t>
+          <t>2026/6/30 00:27:41.020</t>
         </is>
       </c>
       <c r="C334" t="n">
@@ -34895,7 +34895,7 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>2026/6/29 23:27:46.038</t>
+          <t>2026/6/30 00:27:46.038</t>
         </is>
       </c>
       <c r="C335" t="n">
@@ -34998,7 +34998,7 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>2026/6/29 23:27:51.024</t>
+          <t>2026/6/30 00:27:51.024</t>
         </is>
       </c>
       <c r="C336" t="n">
@@ -35101,7 +35101,7 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>2026/6/29 23:27:56.069</t>
+          <t>2026/6/30 00:27:56.069</t>
         </is>
       </c>
       <c r="C337" t="n">
@@ -35204,7 +35204,7 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>2026/6/29 23:28:01.021</t>
+          <t>2026/6/30 00:28:01.021</t>
         </is>
       </c>
       <c r="C338" t="n">
@@ -35307,7 +35307,7 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>2026/6/29 23:28:06.056</t>
+          <t>2026/6/30 00:28:06.056</t>
         </is>
       </c>
       <c r="C339" t="n">
@@ -35410,7 +35410,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>2026/6/29 23:28:11.025</t>
+          <t>2026/6/30 00:28:11.025</t>
         </is>
       </c>
       <c r="C340" t="n">
@@ -35513,7 +35513,7 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>2026/6/29 23:28:16.044</t>
+          <t>2026/6/30 00:28:16.044</t>
         </is>
       </c>
       <c r="C341" t="n">
@@ -35616,7 +35616,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>2026/6/29 23:28:21.049</t>
+          <t>2026/6/30 00:28:21.049</t>
         </is>
       </c>
       <c r="C342" t="n">
@@ -35719,7 +35719,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>2026/6/29 23:28:26.077</t>
+          <t>2026/6/30 00:28:26.077</t>
         </is>
       </c>
       <c r="C343" t="n">
@@ -35822,7 +35822,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>2026/6/29 23:28:31.047</t>
+          <t>2026/6/30 00:28:31.047</t>
         </is>
       </c>
       <c r="C344" t="n">
@@ -35925,7 +35925,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>2026/6/29 23:28:36.068</t>
+          <t>2026/6/30 00:28:36.068</t>
         </is>
       </c>
       <c r="C345" t="n">
@@ -36028,7 +36028,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>2026/6/29 23:28:41.053</t>
+          <t>2026/6/30 00:28:41.053</t>
         </is>
       </c>
       <c r="C346" t="n">
@@ -36131,7 +36131,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>2026/6/29 23:28:46.039</t>
+          <t>2026/6/30 00:28:46.039</t>
         </is>
       </c>
       <c r="C347" t="n">
@@ -36234,7 +36234,7 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>2026/6/29 23:28:51.026</t>
+          <t>2026/6/30 00:28:51.026</t>
         </is>
       </c>
       <c r="C348" t="n">
@@ -36337,7 +36337,7 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>2026/6/29 23:28:56.061</t>
+          <t>2026/6/30 00:28:56.061</t>
         </is>
       </c>
       <c r="C349" t="n">
@@ -36440,7 +36440,7 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>2026/6/29 23:29:01.038</t>
+          <t>2026/6/30 00:29:01.038</t>
         </is>
       </c>
       <c r="C350" t="n">
@@ -36543,7 +36543,7 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>2026/6/29 23:29:06.080</t>
+          <t>2026/6/30 00:29:06.080</t>
         </is>
       </c>
       <c r="C351" t="n">
@@ -36646,7 +36646,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>2026/6/29 23:29:11.061</t>
+          <t>2026/6/30 00:29:11.061</t>
         </is>
       </c>
       <c r="C352" t="n">
@@ -36749,7 +36749,7 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>2026/6/29 23:29:16.056</t>
+          <t>2026/6/30 00:29:16.056</t>
         </is>
       </c>
       <c r="C353" t="n">
@@ -36852,7 +36852,7 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>2026/6/29 23:29:21.072</t>
+          <t>2026/6/30 00:29:21.072</t>
         </is>
       </c>
       <c r="C354" t="n">
@@ -36955,7 +36955,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>2026/6/29 23:29:26.039</t>
+          <t>2026/6/30 00:29:26.039</t>
         </is>
       </c>
       <c r="C355" t="n">
@@ -37058,7 +37058,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>2026/6/29 23:29:31.046</t>
+          <t>2026/6/30 00:29:31.046</t>
         </is>
       </c>
       <c r="C356" t="n">
@@ -37161,7 +37161,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>2026/6/29 23:29:36.090</t>
+          <t>2026/6/30 00:29:36.090</t>
         </is>
       </c>
       <c r="C357" t="n">
@@ -37264,7 +37264,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>2026/6/29 23:29:41.051</t>
+          <t>2026/6/30 00:29:41.051</t>
         </is>
       </c>
       <c r="C358" t="n">
@@ -37367,7 +37367,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>2026/6/29 23:29:46.062</t>
+          <t>2026/6/30 00:29:46.062</t>
         </is>
       </c>
       <c r="C359" t="n">
@@ -37470,7 +37470,7 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>2026/6/29 23:29:51.075</t>
+          <t>2026/6/30 00:29:51.075</t>
         </is>
       </c>
       <c r="C360" t="n">
@@ -37573,7 +37573,7 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>2026/6/29 23:29:56.077</t>
+          <t>2026/6/30 00:29:56.077</t>
         </is>
       </c>
       <c r="C361" t="n">
@@ -37676,7 +37676,7 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>2026/6/29 23:30:01.063</t>
+          <t>2026/6/30 00:30:01.063</t>
         </is>
       </c>
       <c r="C362" t="n">
@@ -37779,7 +37779,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>2026/6/29 23:30:06.059</t>
+          <t>2026/6/30 00:30:06.059</t>
         </is>
       </c>
       <c r="C363" t="n">
@@ -37882,7 +37882,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>2026/6/29 23:30:11.073</t>
+          <t>2026/6/30 00:30:11.073</t>
         </is>
       </c>
       <c r="C364" t="n">
@@ -37985,7 +37985,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>2026/6/29 23:30:16.055</t>
+          <t>2026/6/30 00:30:16.055</t>
         </is>
       </c>
       <c r="C365" t="n">
@@ -38088,7 +38088,7 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>2026/6/29 23:30:21.051</t>
+          <t>2026/6/30 00:30:21.051</t>
         </is>
       </c>
       <c r="C366" t="n">
@@ -38191,7 +38191,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>2026/6/29 23:30:26.080</t>
+          <t>2026/6/30 00:30:26.080</t>
         </is>
       </c>
       <c r="C367" t="n">
@@ -38294,7 +38294,7 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>2026/6/29 23:30:31.092</t>
+          <t>2026/6/30 00:30:31.092</t>
         </is>
       </c>
       <c r="C368" t="n">
@@ -38397,7 +38397,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>2026/6/29 23:30:36.048</t>
+          <t>2026/6/30 00:30:36.048</t>
         </is>
       </c>
       <c r="C369" t="n">
@@ -38500,7 +38500,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>2026/6/29 23:30:41.060</t>
+          <t>2026/6/30 00:30:41.060</t>
         </is>
       </c>
       <c r="C370" t="n">
@@ -38603,7 +38603,7 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>2026/6/29 23:30:46.090</t>
+          <t>2026/6/30 00:30:46.090</t>
         </is>
       </c>
       <c r="C371" t="n">
@@ -38706,7 +38706,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>2026/6/29 23:30:51.054</t>
+          <t>2026/6/30 00:30:51.054</t>
         </is>
       </c>
       <c r="C372" t="n">
@@ -38809,7 +38809,7 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>2026/6/29 23:30:56.067</t>
+          <t>2026/6/30 00:30:56.067</t>
         </is>
       </c>
       <c r="C373" t="n">
@@ -38912,7 +38912,7 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>2026/6/29 23:31:01.068</t>
+          <t>2026/6/30 00:31:01.068</t>
         </is>
       </c>
       <c r="C374" t="n">
@@ -39015,7 +39015,7 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>2026/6/29 23:31:06.107</t>
+          <t>2026/6/30 00:31:06.107</t>
         </is>
       </c>
       <c r="C375" t="n">
@@ -39118,7 +39118,7 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>2026/6/29 23:31:11.057</t>
+          <t>2026/6/30 00:31:11.057</t>
         </is>
       </c>
       <c r="C376" t="n">
@@ -39221,7 +39221,7 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>2026/6/29 23:31:16.078</t>
+          <t>2026/6/30 00:31:16.078</t>
         </is>
       </c>
       <c r="C377" t="n">
@@ -39324,7 +39324,7 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>2026/6/29 23:31:21.050</t>
+          <t>2026/6/30 00:31:21.050</t>
         </is>
       </c>
       <c r="C378" t="n">
@@ -39427,7 +39427,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>2026/6/29 23:31:26.059</t>
+          <t>2026/6/30 00:31:26.059</t>
         </is>
       </c>
       <c r="C379" t="n">
@@ -39530,7 +39530,7 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>2026/6/29 23:31:31.056</t>
+          <t>2026/6/30 00:31:31.056</t>
         </is>
       </c>
       <c r="C380" t="n">
@@ -39633,7 +39633,7 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>2026/6/29 23:31:36.104</t>
+          <t>2026/6/30 00:31:36.104</t>
         </is>
       </c>
       <c r="C381" t="n">
@@ -39736,7 +39736,7 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>2026/6/29 23:31:41.062</t>
+          <t>2026/6/30 00:31:41.062</t>
         </is>
       </c>
       <c r="C382" t="n">
@@ -39839,7 +39839,7 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>2026/6/29 23:31:46.099</t>
+          <t>2026/6/30 00:31:46.099</t>
         </is>
       </c>
       <c r="C383" t="n">
@@ -39942,7 +39942,7 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>2026/6/29 23:31:51.103</t>
+          <t>2026/6/30 00:31:51.103</t>
         </is>
       </c>
       <c r="C384" t="n">
@@ -40045,7 +40045,7 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>2026/6/29 23:31:56.089</t>
+          <t>2026/6/30 00:31:56.089</t>
         </is>
       </c>
       <c r="C385" t="n">
@@ -40148,7 +40148,7 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>2026/6/29 23:32:01.094</t>
+          <t>2026/6/30 00:32:01.094</t>
         </is>
       </c>
       <c r="C386" t="n">
@@ -40251,7 +40251,7 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>2026/6/29 23:32:06.086</t>
+          <t>2026/6/30 00:32:06.086</t>
         </is>
       </c>
       <c r="C387" t="n">
@@ -40354,7 +40354,7 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>2026/6/29 23:32:11.081</t>
+          <t>2026/6/30 00:32:11.081</t>
         </is>
       </c>
       <c r="C388" t="n">
@@ -40457,7 +40457,7 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>2026/6/29 23:32:16.085</t>
+          <t>2026/6/30 00:32:16.085</t>
         </is>
       </c>
       <c r="C389" t="n">
@@ -40560,7 +40560,7 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>2026/6/29 23:32:21.096</t>
+          <t>2026/6/30 00:32:21.096</t>
         </is>
       </c>
       <c r="C390" t="n">
@@ -40663,7 +40663,7 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>2026/6/29 23:32:26.088</t>
+          <t>2026/6/30 00:32:26.088</t>
         </is>
       </c>
       <c r="C391" t="n">
@@ -40766,7 +40766,7 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>2026/6/29 23:32:31.077</t>
+          <t>2026/6/30 00:32:31.077</t>
         </is>
       </c>
       <c r="C392" t="n">
@@ -40869,7 +40869,7 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>2026/6/29 23:32:36.065</t>
+          <t>2026/6/30 00:32:36.065</t>
         </is>
       </c>
       <c r="C393" t="n">
@@ -40972,7 +40972,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>2026/6/29 23:32:41.103</t>
+          <t>2026/6/30 00:32:41.103</t>
         </is>
       </c>
       <c r="C394" t="n">
@@ -41075,7 +41075,7 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>2026/6/29 23:32:46.108</t>
+          <t>2026/6/30 00:32:46.108</t>
         </is>
       </c>
       <c r="C395" t="n">
@@ -41178,7 +41178,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>2026/6/29 23:32:51.115</t>
+          <t>2026/6/30 00:32:51.115</t>
         </is>
       </c>
       <c r="C396" t="n">
@@ -41281,7 +41281,7 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>2026/6/29 23:32:56.092</t>
+          <t>2026/6/30 00:32:56.092</t>
         </is>
       </c>
       <c r="C397" t="n">
@@ -41384,7 +41384,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>2026/6/29 23:33:01.064</t>
+          <t>2026/6/30 00:33:01.064</t>
         </is>
       </c>
       <c r="C398" t="n">
@@ -41487,7 +41487,7 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>2026/6/29 23:33:06.072</t>
+          <t>2026/6/30 00:33:06.072</t>
         </is>
       </c>
       <c r="C399" t="n">
@@ -41590,7 +41590,7 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>2026/6/29 23:33:11.106</t>
+          <t>2026/6/30 00:33:11.106</t>
         </is>
       </c>
       <c r="C400" t="n">
@@ -41693,7 +41693,7 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>2026/6/29 23:33:16.129</t>
+          <t>2026/6/30 00:33:16.129</t>
         </is>
       </c>
       <c r="C401" t="n">
@@ -41796,7 +41796,7 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>2026/6/29 23:33:21.102</t>
+          <t>2026/6/30 00:33:21.102</t>
         </is>
       </c>
       <c r="C402" t="n">
@@ -41899,7 +41899,7 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>2026/6/29 23:33:26.081</t>
+          <t>2026/6/30 00:33:26.081</t>
         </is>
       </c>
       <c r="C403" t="n">
@@ -42002,7 +42002,7 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>2026/6/29 23:33:31.099</t>
+          <t>2026/6/30 00:33:31.099</t>
         </is>
       </c>
       <c r="C404" t="n">
@@ -42105,7 +42105,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>2026/6/29 23:33:36.104</t>
+          <t>2026/6/30 00:33:36.104</t>
         </is>
       </c>
       <c r="C405" t="n">
@@ -42208,7 +42208,7 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>2026/6/29 23:33:41.122</t>
+          <t>2026/6/30 00:33:41.122</t>
         </is>
       </c>
       <c r="C406" t="n">
@@ -42311,7 +42311,7 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>2026/6/29 23:33:46.084</t>
+          <t>2026/6/30 00:33:46.084</t>
         </is>
       </c>
       <c r="C407" t="n">
@@ -42414,7 +42414,7 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>2026/6/29 23:33:51.092</t>
+          <t>2026/6/30 00:33:51.092</t>
         </is>
       </c>
       <c r="C408" t="n">
@@ -42517,7 +42517,7 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>2026/6/29 23:33:56.085</t>
+          <t>2026/6/30 00:33:56.085</t>
         </is>
       </c>
       <c r="C409" t="n">
@@ -42620,7 +42620,7 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>2026/6/29 23:34:01.084</t>
+          <t>2026/6/30 00:34:01.084</t>
         </is>
       </c>
       <c r="C410" t="n">
@@ -42723,7 +42723,7 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>2026/6/29 23:34:06.122</t>
+          <t>2026/6/30 00:34:06.122</t>
         </is>
       </c>
       <c r="C411" t="n">
@@ -42826,7 +42826,7 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>2026/6/29 23:34:11.088</t>
+          <t>2026/6/30 00:34:11.088</t>
         </is>
       </c>
       <c r="C412" t="n">
@@ -42929,7 +42929,7 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>2026/6/29 23:34:16.100</t>
+          <t>2026/6/30 00:34:16.100</t>
         </is>
       </c>
       <c r="C413" t="n">
@@ -43032,7 +43032,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>2026/6/29 23:34:21.106</t>
+          <t>2026/6/30 00:34:21.106</t>
         </is>
       </c>
       <c r="C414" t="n">
@@ -43135,7 +43135,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>2026/6/29 23:34:26.106</t>
+          <t>2026/6/30 00:34:26.106</t>
         </is>
       </c>
       <c r="C415" t="n">
@@ -43238,7 +43238,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>2026/6/29 23:34:31.116</t>
+          <t>2026/6/30 00:34:31.116</t>
         </is>
       </c>
       <c r="C416" t="n">
@@ -43341,7 +43341,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>2026/6/29 23:34:36.108</t>
+          <t>2026/6/30 00:34:36.108</t>
         </is>
       </c>
       <c r="C417" t="n">
@@ -43444,7 +43444,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>2026/6/29 23:34:41.126</t>
+          <t>2026/6/30 00:34:41.126</t>
         </is>
       </c>
       <c r="C418" t="n">
@@ -43547,7 +43547,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>2026/6/29 23:34:46.123</t>
+          <t>2026/6/30 00:34:46.123</t>
         </is>
       </c>
       <c r="C419" t="n">
@@ -43650,7 +43650,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>2026/6/29 23:34:51.105</t>
+          <t>2026/6/30 00:34:51.105</t>
         </is>
       </c>
       <c r="C420" t="n">
@@ -43753,7 +43753,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>2026/6/29 23:34:56.132</t>
+          <t>2026/6/30 00:34:56.132</t>
         </is>
       </c>
       <c r="C421" t="n">
@@ -43856,7 +43856,7 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>2026/6/29 23:35:01.124</t>
+          <t>2026/6/30 00:35:01.124</t>
         </is>
       </c>
       <c r="C422" t="n">
@@ -43959,7 +43959,7 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>2026/6/29 23:35:06.139</t>
+          <t>2026/6/30 00:35:06.139</t>
         </is>
       </c>
       <c r="C423" t="n">
@@ -44062,7 +44062,7 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>2026/6/29 23:35:11.137</t>
+          <t>2026/6/30 00:35:11.137</t>
         </is>
       </c>
       <c r="C424" t="n">
@@ -44165,7 +44165,7 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>2026/6/29 23:35:16.100</t>
+          <t>2026/6/30 00:35:16.100</t>
         </is>
       </c>
       <c r="C425" t="n">
@@ -44268,7 +44268,7 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>2026/6/29 23:35:21.103</t>
+          <t>2026/6/30 00:35:21.103</t>
         </is>
       </c>
       <c r="C426" t="n">
@@ -44371,7 +44371,7 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>2026/6/29 23:35:26.120</t>
+          <t>2026/6/30 00:35:26.120</t>
         </is>
       </c>
       <c r="C427" t="n">
@@ -44474,7 +44474,7 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>2026/6/29 23:35:31.111</t>
+          <t>2026/6/30 00:35:31.111</t>
         </is>
       </c>
       <c r="C428" t="n">
@@ -44577,7 +44577,7 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>2026/6/29 23:35:36.128</t>
+          <t>2026/6/30 00:35:36.128</t>
         </is>
       </c>
       <c r="C429" t="n">
@@ -44680,7 +44680,7 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>2026/6/29 23:35:41.143</t>
+          <t>2026/6/30 00:35:41.143</t>
         </is>
       </c>
       <c r="C430" t="n">
@@ -44783,7 +44783,7 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>2026/6/29 23:35:46.110</t>
+          <t>2026/6/30 00:35:46.110</t>
         </is>
       </c>
       <c r="C431" t="n">
@@ -44886,7 +44886,7 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>2026/6/29 23:35:51.119</t>
+          <t>2026/6/30 00:35:51.119</t>
         </is>
       </c>
       <c r="C432" t="n">
@@ -44989,7 +44989,7 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>2026/6/29 23:35:56.138</t>
+          <t>2026/6/30 00:35:56.138</t>
         </is>
       </c>
       <c r="C433" t="n">
@@ -45092,7 +45092,7 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>2026/6/29 23:36:01.159</t>
+          <t>2026/6/30 00:36:01.159</t>
         </is>
       </c>
       <c r="C434" t="n">
@@ -45195,7 +45195,7 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>2026/6/29 23:36:06.139</t>
+          <t>2026/6/30 00:36:06.139</t>
         </is>
       </c>
       <c r="C435" t="n">
@@ -45298,7 +45298,7 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>2026/6/29 23:36:11.165</t>
+          <t>2026/6/30 00:36:11.165</t>
         </is>
       </c>
       <c r="C436" t="n">
@@ -45401,7 +45401,7 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>2026/6/29 23:36:16.127</t>
+          <t>2026/6/30 00:36:16.127</t>
         </is>
       </c>
       <c r="C437" t="n">
@@ -45504,7 +45504,7 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>2026/6/29 23:36:21.160</t>
+          <t>2026/6/30 00:36:21.160</t>
         </is>
       </c>
       <c r="C438" t="n">
@@ -45607,7 +45607,7 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>2026/6/29 23:36:26.162</t>
+          <t>2026/6/30 00:36:26.162</t>
         </is>
       </c>
       <c r="C439" t="n">
@@ -45710,7 +45710,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>2026/6/29 23:36:31.136</t>
+          <t>2026/6/30 00:36:31.136</t>
         </is>
       </c>
       <c r="C440" t="n">
@@ -45813,7 +45813,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>2026/6/29 23:36:36.158</t>
+          <t>2026/6/30 00:36:36.158</t>
         </is>
       </c>
       <c r="C441" t="n">
@@ -45916,7 +45916,7 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>2026/6/29 23:36:41.132</t>
+          <t>2026/6/30 00:36:41.132</t>
         </is>
       </c>
       <c r="C442" t="n">
@@ -46019,7 +46019,7 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>2026/6/29 23:36:46.152</t>
+          <t>2026/6/30 00:36:46.152</t>
         </is>
       </c>
       <c r="C443" t="n">
@@ -46122,7 +46122,7 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>2026/6/29 23:36:51.154</t>
+          <t>2026/6/30 00:36:51.154</t>
         </is>
       </c>
       <c r="C444" t="n">
@@ -46225,7 +46225,7 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>2026/6/29 23:36:56.146</t>
+          <t>2026/6/30 00:36:56.146</t>
         </is>
       </c>
       <c r="C445" t="n">
@@ -46328,7 +46328,7 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>2026/6/29 23:37:01.125</t>
+          <t>2026/6/30 00:37:01.125</t>
         </is>
       </c>
       <c r="C446" t="n">
@@ -46431,7 +46431,7 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>2026/6/29 23:37:06.161</t>
+          <t>2026/6/30 00:37:06.161</t>
         </is>
       </c>
       <c r="C447" t="n">
@@ -46534,7 +46534,7 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>2026/6/29 23:37:11.160</t>
+          <t>2026/6/30 00:37:11.160</t>
         </is>
       </c>
       <c r="C448" t="n">
@@ -46637,7 +46637,7 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>2026/6/29 23:37:16.134</t>
+          <t>2026/6/30 00:37:16.134</t>
         </is>
       </c>
       <c r="C449" t="n">
@@ -46740,7 +46740,7 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>2026/6/29 23:37:21.156</t>
+          <t>2026/6/30 00:37:21.156</t>
         </is>
       </c>
       <c r="C450" t="n">
@@ -46843,7 +46843,7 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>2026/6/29 23:37:26.132</t>
+          <t>2026/6/30 00:37:26.132</t>
         </is>
       </c>
       <c r="C451" t="n">
@@ -46946,7 +46946,7 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>2026/6/29 23:37:31.162</t>
+          <t>2026/6/30 00:37:31.162</t>
         </is>
       </c>
       <c r="C452" t="n">
@@ -47049,7 +47049,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>2026/6/29 23:37:36.127</t>
+          <t>2026/6/30 00:37:36.127</t>
         </is>
       </c>
       <c r="C453" t="n">
@@ -47152,7 +47152,7 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>2026/6/29 23:37:41.122</t>
+          <t>2026/6/30 00:37:41.122</t>
         </is>
       </c>
       <c r="C454" t="n">
@@ -47255,7 +47255,7 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>2026/6/29 23:37:46.169</t>
+          <t>2026/6/30 00:37:46.169</t>
         </is>
       </c>
       <c r="C455" t="n">
@@ -47358,7 +47358,7 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>2026/6/29 23:37:51.178</t>
+          <t>2026/6/30 00:37:51.178</t>
         </is>
       </c>
       <c r="C456" t="n">
@@ -47461,7 +47461,7 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>2026/6/29 23:37:56.140</t>
+          <t>2026/6/30 00:37:56.140</t>
         </is>
       </c>
       <c r="C457" t="n">
@@ -47564,7 +47564,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>2026/6/29 23:38:01.127</t>
+          <t>2026/6/30 00:38:01.127</t>
         </is>
       </c>
       <c r="C458" t="n">
@@ -47667,7 +47667,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>2026/6/29 23:38:06.138</t>
+          <t>2026/6/30 00:38:06.138</t>
         </is>
       </c>
       <c r="C459" t="n">
@@ -47770,7 +47770,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>2026/6/29 23:38:11.150</t>
+          <t>2026/6/30 00:38:11.150</t>
         </is>
       </c>
       <c r="C460" t="n">
@@ -47873,7 +47873,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>2026/6/29 23:38:16.161</t>
+          <t>2026/6/30 00:38:16.161</t>
         </is>
       </c>
       <c r="C461" t="n">
@@ -47976,7 +47976,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>2026/6/29 23:38:21.183</t>
+          <t>2026/6/30 00:38:21.183</t>
         </is>
       </c>
       <c r="C462" t="n">
@@ -48079,7 +48079,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>2026/6/29 23:38:26.161</t>
+          <t>2026/6/30 00:38:26.161</t>
         </is>
       </c>
       <c r="C463" t="n">
@@ -48182,7 +48182,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>2026/6/29 23:38:31.140</t>
+          <t>2026/6/30 00:38:31.140</t>
         </is>
       </c>
       <c r="C464" t="n">
@@ -48285,7 +48285,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>2026/6/29 23:38:36.169</t>
+          <t>2026/6/30 00:38:36.169</t>
         </is>
       </c>
       <c r="C465" t="n">
@@ -48388,7 +48388,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>2026/6/29 23:38:41.183</t>
+          <t>2026/6/30 00:38:41.183</t>
         </is>
       </c>
       <c r="C466" t="n">
@@ -48491,7 +48491,7 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>2026/6/29 23:38:46.149</t>
+          <t>2026/6/30 00:38:46.149</t>
         </is>
       </c>
       <c r="C467" t="n">
@@ -48594,7 +48594,7 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>2026/6/29 23:38:51.156</t>
+          <t>2026/6/30 00:38:51.156</t>
         </is>
       </c>
       <c r="C468" t="n">
@@ -48697,7 +48697,7 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>2026/6/29 23:38:56.156</t>
+          <t>2026/6/30 00:38:56.156</t>
         </is>
       </c>
       <c r="C469" t="n">
@@ -48800,7 +48800,7 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>2026/6/29 23:39:01.139</t>
+          <t>2026/6/30 00:39:01.139</t>
         </is>
       </c>
       <c r="C470" t="n">
@@ -48903,7 +48903,7 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>2026/6/29 23:39:06.160</t>
+          <t>2026/6/30 00:39:06.160</t>
         </is>
       </c>
       <c r="C471" t="n">
@@ -49006,7 +49006,7 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>2026/6/29 23:39:11.184</t>
+          <t>2026/6/30 00:39:11.184</t>
         </is>
       </c>
       <c r="C472" t="n">
@@ -49109,7 +49109,7 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>2026/6/29 23:39:16.174</t>
+          <t>2026/6/30 00:39:16.174</t>
         </is>
       </c>
       <c r="C473" t="n">
@@ -49212,7 +49212,7 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>2026/6/29 23:39:21.180</t>
+          <t>2026/6/30 00:39:21.180</t>
         </is>
       </c>
       <c r="C474" t="n">
@@ -49315,7 +49315,7 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>2026/6/29 23:39:26.141</t>
+          <t>2026/6/30 00:39:26.141</t>
         </is>
       </c>
       <c r="C475" t="n">
@@ -49418,7 +49418,7 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>2026/6/29 23:39:31.196</t>
+          <t>2026/6/30 00:39:31.196</t>
         </is>
       </c>
       <c r="C476" t="n">
@@ -49521,7 +49521,7 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>2026/6/29 23:39:36.182</t>
+          <t>2026/6/30 00:39:36.182</t>
         </is>
       </c>
       <c r="C477" t="n">
@@ -49624,7 +49624,7 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>2026/6/29 23:39:41.182</t>
+          <t>2026/6/30 00:39:41.182</t>
         </is>
       </c>
       <c r="C478" t="n">
@@ -49727,7 +49727,7 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>2026/6/29 23:39:46.188</t>
+          <t>2026/6/30 00:39:46.188</t>
         </is>
       </c>
       <c r="C479" t="n">
@@ -49830,7 +49830,7 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>2026/6/29 23:39:51.150</t>
+          <t>2026/6/30 00:39:51.150</t>
         </is>
       </c>
       <c r="C480" t="n">
@@ -49933,7 +49933,7 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>2026/6/29 23:39:56.185</t>
+          <t>2026/6/30 00:39:56.185</t>
         </is>
       </c>
       <c r="C481" t="n">
@@ -50036,7 +50036,7 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>2026/6/29 23:40:01.176</t>
+          <t>2026/6/30 00:40:01.176</t>
         </is>
       </c>
       <c r="C482" t="n">
@@ -50139,7 +50139,7 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>2026/6/29 23:40:06.150</t>
+          <t>2026/6/30 00:40:06.150</t>
         </is>
       </c>
       <c r="C483" t="n">
@@ -50242,7 +50242,7 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>2026/6/29 23:40:11.185</t>
+          <t>2026/6/30 00:40:11.185</t>
         </is>
       </c>
       <c r="C484" t="n">
@@ -50345,7 +50345,7 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>2026/6/29 23:40:16.174</t>
+          <t>2026/6/30 00:40:16.174</t>
         </is>
       </c>
       <c r="C485" t="n">
@@ -50448,7 +50448,7 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>2026/6/29 23:40:21.150</t>
+          <t>2026/6/30 00:40:21.150</t>
         </is>
       </c>
       <c r="C486" t="n">
@@ -50551,7 +50551,7 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>2026/6/29 23:40:26.163</t>
+          <t>2026/6/30 00:40:26.163</t>
         </is>
       </c>
       <c r="C487" t="n">
@@ -50654,7 +50654,7 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>2026/6/29 23:40:31.174</t>
+          <t>2026/6/30 00:40:31.174</t>
         </is>
       </c>
       <c r="C488" t="n">
@@ -50757,7 +50757,7 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>2026/6/29 23:40:36.162</t>
+          <t>2026/6/30 00:40:36.162</t>
         </is>
       </c>
       <c r="C489" t="n">
@@ -50860,7 +50860,7 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>2026/6/29 23:40:41.189</t>
+          <t>2026/6/30 00:40:41.189</t>
         </is>
       </c>
       <c r="C490" t="n">
@@ -50963,7 +50963,7 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>2026/6/29 23:40:46.167</t>
+          <t>2026/6/30 00:40:46.167</t>
         </is>
       </c>
       <c r="C491" t="n">
@@ -51066,7 +51066,7 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>2026/6/29 23:40:51.183</t>
+          <t>2026/6/30 00:40:51.183</t>
         </is>
       </c>
       <c r="C492" t="n">
@@ -51169,7 +51169,7 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>2026/6/29 23:40:56.196</t>
+          <t>2026/6/30 00:40:56.196</t>
         </is>
       </c>
       <c r="C493" t="n">
@@ -51272,7 +51272,7 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>2026/6/29 23:41:01.196</t>
+          <t>2026/6/30 00:41:01.196</t>
         </is>
       </c>
       <c r="C494" t="n">
@@ -51375,7 +51375,7 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>2026/6/29 23:41:06.181</t>
+          <t>2026/6/30 00:41:06.181</t>
         </is>
       </c>
       <c r="C495" t="n">
@@ -51478,7 +51478,7 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>2026/6/29 23:41:11.207</t>
+          <t>2026/6/30 00:41:11.207</t>
         </is>
       </c>
       <c r="C496" t="n">
@@ -51581,7 +51581,7 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>2026/6/29 23:41:16.207</t>
+          <t>2026/6/30 00:41:16.207</t>
         </is>
       </c>
       <c r="C497" t="n">
@@ -51684,7 +51684,7 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>2026/6/29 23:41:21.181</t>
+          <t>2026/6/30 00:41:21.181</t>
         </is>
       </c>
       <c r="C498" t="n">
@@ -51787,7 +51787,7 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>2026/6/29 23:41:26.164</t>
+          <t>2026/6/30 00:41:26.164</t>
         </is>
       </c>
       <c r="C499" t="n">
@@ -51890,7 +51890,7 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>2026/6/29 23:41:31.216</t>
+          <t>2026/6/30 00:41:31.216</t>
         </is>
       </c>
       <c r="C500" t="n">
@@ -51993,7 +51993,7 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>2026/6/29 23:41:36.194</t>
+          <t>2026/6/30 00:41:36.194</t>
         </is>
       </c>
       <c r="C501" t="n">
@@ -52096,7 +52096,7 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>2026/6/29 23:41:41.172</t>
+          <t>2026/6/30 00:41:41.172</t>
         </is>
       </c>
       <c r="C502" t="n">
@@ -52199,7 +52199,7 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>2026/6/29 23:41:46.192</t>
+          <t>2026/6/30 00:41:46.192</t>
         </is>
       </c>
       <c r="C503" t="n">
@@ -52302,7 +52302,7 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>2026/6/29 23:41:51.181</t>
+          <t>2026/6/30 00:41:51.181</t>
         </is>
       </c>
       <c r="C504" t="n">
@@ -52405,7 +52405,7 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>2026/6/29 23:41:56.173</t>
+          <t>2026/6/30 00:41:56.173</t>
         </is>
       </c>
       <c r="C505" t="n">
@@ -52508,7 +52508,7 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>2026/6/29 23:42:01.205</t>
+          <t>2026/6/30 00:42:01.205</t>
         </is>
       </c>
       <c r="C506" t="n">
@@ -52611,7 +52611,7 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>2026/6/29 23:42:06.183</t>
+          <t>2026/6/30 00:42:06.183</t>
         </is>
       </c>
       <c r="C507" t="n">
@@ -52714,7 +52714,7 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>2026/6/29 23:42:11.173</t>
+          <t>2026/6/30 00:42:11.173</t>
         </is>
       </c>
       <c r="C508" t="n">
@@ -52817,7 +52817,7 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>2026/6/29 23:42:16.162</t>
+          <t>2026/6/30 00:42:16.162</t>
         </is>
       </c>
       <c r="C509" t="n">
@@ -52920,7 +52920,7 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>2026/6/29 23:42:21.209</t>
+          <t>2026/6/30 00:42:21.209</t>
         </is>
       </c>
       <c r="C510" t="n">
@@ -53023,7 +53023,7 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>2026/6/29 23:42:26.183</t>
+          <t>2026/6/30 00:42:26.183</t>
         </is>
       </c>
       <c r="C511" t="n">
@@ -53126,7 +53126,7 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>2026/6/29 23:42:31.209</t>
+          <t>2026/6/30 00:42:31.209</t>
         </is>
       </c>
       <c r="C512" t="n">
@@ -53229,7 +53229,7 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>2026/6/29 23:42:36.186</t>
+          <t>2026/6/30 00:42:36.186</t>
         </is>
       </c>
       <c r="C513" t="n">
@@ -53332,7 +53332,7 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>2026/6/29 23:42:41.200</t>
+          <t>2026/6/30 00:42:41.200</t>
         </is>
       </c>
       <c r="C514" t="n">
@@ -53435,7 +53435,7 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>2026/6/29 23:42:46.187</t>
+          <t>2026/6/30 00:42:46.187</t>
         </is>
       </c>
       <c r="C515" t="n">
@@ -53538,7 +53538,7 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>2026/6/29 23:42:51.179</t>
+          <t>2026/6/30 00:42:51.179</t>
         </is>
       </c>
       <c r="C516" t="n">
@@ -53641,7 +53641,7 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>2026/6/29 23:42:56.202</t>
+          <t>2026/6/30 00:42:56.202</t>
         </is>
       </c>
       <c r="C517" t="n">
@@ -53744,7 +53744,7 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>2026/6/29 23:43:01.206</t>
+          <t>2026/6/30 00:43:01.206</t>
         </is>
       </c>
       <c r="C518" t="n">
@@ -53847,7 +53847,7 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>2026/6/29 23:43:06.188</t>
+          <t>2026/6/30 00:43:06.188</t>
         </is>
       </c>
       <c r="C519" t="n">
@@ -53950,7 +53950,7 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>2026/6/29 23:43:11.187</t>
+          <t>2026/6/30 00:43:11.187</t>
         </is>
       </c>
       <c r="C520" t="n">
@@ -54053,7 +54053,7 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>2026/6/29 23:43:16.226</t>
+          <t>2026/6/30 00:43:16.226</t>
         </is>
       </c>
       <c r="C521" t="n">
@@ -54156,7 +54156,7 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>2026/6/29 23:43:21.206</t>
+          <t>2026/6/30 00:43:21.206</t>
         </is>
       </c>
       <c r="C522" t="n">
@@ -54259,7 +54259,7 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>2026/6/29 23:43:26.226</t>
+          <t>2026/6/30 00:43:26.226</t>
         </is>
       </c>
       <c r="C523" t="n">
@@ -54362,7 +54362,7 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>2026/6/29 23:43:31.208</t>
+          <t>2026/6/30 00:43:31.208</t>
         </is>
       </c>
       <c r="C524" t="n">
@@ -54465,7 +54465,7 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>2026/6/29 23:43:36.214</t>
+          <t>2026/6/30 00:43:36.214</t>
         </is>
       </c>
       <c r="C525" t="n">
@@ -54568,7 +54568,7 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>2026/6/29 23:43:41.183</t>
+          <t>2026/6/30 00:43:41.183</t>
         </is>
       </c>
       <c r="C526" t="n">
@@ -54671,7 +54671,7 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>2026/6/29 23:43:46.174</t>
+          <t>2026/6/30 00:43:46.174</t>
         </is>
       </c>
       <c r="C527" t="n">
@@ -54774,7 +54774,7 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>2026/6/29 23:43:51.208</t>
+          <t>2026/6/30 00:43:51.208</t>
         </is>
       </c>
       <c r="C528" t="n">
@@ -54877,7 +54877,7 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>2026/6/29 23:43:56.225</t>
+          <t>2026/6/30 00:43:56.225</t>
         </is>
       </c>
       <c r="C529" t="n">
@@ -54980,7 +54980,7 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>2026/6/29 23:44:01.231</t>
+          <t>2026/6/30 00:44:01.231</t>
         </is>
       </c>
       <c r="C530" t="n">
@@ -55083,7 +55083,7 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>2026/6/29 23:44:06.215</t>
+          <t>2026/6/30 00:44:06.215</t>
         </is>
       </c>
       <c r="C531" t="n">
@@ -55186,7 +55186,7 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>2026/6/29 23:44:11.237</t>
+          <t>2026/6/30 00:44:11.237</t>
         </is>
       </c>
       <c r="C532" t="n">
@@ -55289,7 +55289,7 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>2026/6/29 23:44:16.195</t>
+          <t>2026/6/30 00:44:16.195</t>
         </is>
       </c>
       <c r="C533" t="n">
@@ -55392,7 +55392,7 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>2026/6/29 23:44:21.220</t>
+          <t>2026/6/30 00:44:21.220</t>
         </is>
       </c>
       <c r="C534" t="n">
@@ -55495,7 +55495,7 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>2026/6/29 23:44:26.207</t>
+          <t>2026/6/30 00:44:26.207</t>
         </is>
       </c>
       <c r="C535" t="n">
@@ -55598,7 +55598,7 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>2026/6/29 23:44:31.218</t>
+          <t>2026/6/30 00:44:31.218</t>
         </is>
       </c>
       <c r="C536" t="n">
@@ -55701,7 +55701,7 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>2026/6/29 23:44:36.195</t>
+          <t>2026/6/30 00:44:36.195</t>
         </is>
       </c>
       <c r="C537" t="n">
@@ -55804,7 +55804,7 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>2026/6/29 23:44:41.224</t>
+          <t>2026/6/30 00:44:41.224</t>
         </is>
       </c>
       <c r="C538" t="n">
@@ -55907,7 +55907,7 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>2026/6/29 23:44:46.230</t>
+          <t>2026/6/30 00:44:46.230</t>
         </is>
       </c>
       <c r="C539" t="n">
@@ -56010,7 +56010,7 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>2026/6/29 23:44:51.251</t>
+          <t>2026/6/30 00:44:51.251</t>
         </is>
       </c>
       <c r="C540" t="n">
@@ -56113,7 +56113,7 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>2026/6/29 23:44:56.222</t>
+          <t>2026/6/30 00:44:56.222</t>
         </is>
       </c>
       <c r="C541" t="n">
@@ -56216,7 +56216,7 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>2026/6/29 23:45:01.212</t>
+          <t>2026/6/30 00:45:01.212</t>
         </is>
       </c>
       <c r="C542" t="n">
@@ -56319,7 +56319,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>2026/6/29 23:45:06.214</t>
+          <t>2026/6/30 00:45:06.214</t>
         </is>
       </c>
       <c r="C543" t="n">
@@ -56422,7 +56422,7 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>2026/6/29 23:45:11.236</t>
+          <t>2026/6/30 00:45:11.236</t>
         </is>
       </c>
       <c r="C544" t="n">
@@ -56525,7 +56525,7 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>2026/6/29 23:45:16.239</t>
+          <t>2026/6/30 00:45:16.239</t>
         </is>
       </c>
       <c r="C545" t="n">
@@ -56628,7 +56628,7 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>2026/6/29 23:45:21.235</t>
+          <t>2026/6/30 00:45:21.235</t>
         </is>
       </c>
       <c r="C546" t="n">
@@ -56731,7 +56731,7 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>2026/6/29 23:45:26.240</t>
+          <t>2026/6/30 00:45:26.240</t>
         </is>
       </c>
       <c r="C547" t="n">
@@ -56834,7 +56834,7 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>2026/6/29 23:45:31.212</t>
+          <t>2026/6/30 00:45:31.212</t>
         </is>
       </c>
       <c r="C548" t="n">
@@ -56937,7 +56937,7 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>2026/6/29 23:45:36.250</t>
+          <t>2026/6/30 00:45:36.250</t>
         </is>
       </c>
       <c r="C549" t="n">
@@ -57040,7 +57040,7 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>2026/6/29 23:45:41.205</t>
+          <t>2026/6/30 00:45:41.205</t>
         </is>
       </c>
       <c r="C550" t="n">
@@ -57143,7 +57143,7 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>2026/6/29 23:45:46.207</t>
+          <t>2026/6/30 00:45:46.207</t>
         </is>
       </c>
       <c r="C551" t="n">
@@ -57246,7 +57246,7 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>2026/6/29 23:45:51.220</t>
+          <t>2026/6/30 00:45:51.220</t>
         </is>
       </c>
       <c r="C552" t="n">
@@ -57349,7 +57349,7 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>2026/6/29 23:45:56.235</t>
+          <t>2026/6/30 00:45:56.235</t>
         </is>
       </c>
       <c r="C553" t="n">
@@ -57452,7 +57452,7 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>2026/6/29 23:46:01.218</t>
+          <t>2026/6/30 00:46:01.218</t>
         </is>
       </c>
       <c r="C554" t="n">
@@ -57555,7 +57555,7 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>2026/6/29 23:46:06.254</t>
+          <t>2026/6/30 00:46:06.254</t>
         </is>
       </c>
       <c r="C555" t="n">
@@ -57658,7 +57658,7 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>2026/6/29 23:46:11.217</t>
+          <t>2026/6/30 00:46:11.217</t>
         </is>
       </c>
       <c r="C556" t="n">
@@ -57761,7 +57761,7 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>2026/6/29 23:46:16.198</t>
+          <t>2026/6/30 00:46:16.198</t>
         </is>
       </c>
       <c r="C557" t="n">
@@ -57864,7 +57864,7 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>2026/6/29 23:46:21.213</t>
+          <t>2026/6/30 00:46:21.213</t>
         </is>
       </c>
       <c r="C558" t="n">
@@ -57967,7 +57967,7 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>2026/6/29 23:46:26.230</t>
+          <t>2026/6/30 00:46:26.230</t>
         </is>
       </c>
       <c r="C559" t="n">
@@ -58070,7 +58070,7 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>2026/6/29 23:46:31.246</t>
+          <t>2026/6/30 00:46:31.246</t>
         </is>
       </c>
       <c r="C560" t="n">
@@ -58173,7 +58173,7 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>2026/6/29 23:46:36.223</t>
+          <t>2026/6/30 00:46:36.223</t>
         </is>
       </c>
       <c r="C561" t="n">
@@ -58276,7 +58276,7 @@
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>2026/6/29 23:46:41.243</t>
+          <t>2026/6/30 00:46:41.243</t>
         </is>
       </c>
       <c r="C562" t="n">
@@ -58379,7 +58379,7 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>2026/6/29 23:46:46.209</t>
+          <t>2026/6/30 00:46:46.209</t>
         </is>
       </c>
       <c r="C563" t="n">
@@ -58482,7 +58482,7 @@
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>2026/6/29 23:46:51.228</t>
+          <t>2026/6/30 00:46:51.228</t>
         </is>
       </c>
       <c r="C564" t="n">
@@ -58585,7 +58585,7 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>2026/6/29 23:46:56.225</t>
+          <t>2026/6/30 00:46:56.225</t>
         </is>
       </c>
       <c r="C565" t="n">
@@ -58688,7 +58688,7 @@
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>2026/6/29 23:47:01.234</t>
+          <t>2026/6/30 00:47:01.234</t>
         </is>
       </c>
       <c r="C566" t="n">
@@ -58791,7 +58791,7 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>2026/6/29 23:47:06.230</t>
+          <t>2026/6/30 00:47:06.230</t>
         </is>
       </c>
       <c r="C567" t="n">
@@ -58894,7 +58894,7 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>2026/6/29 23:47:11.247</t>
+          <t>2026/6/30 00:47:11.247</t>
         </is>
       </c>
       <c r="C568" t="n">
@@ -58997,7 +58997,7 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>2026/6/29 23:47:16.251</t>
+          <t>2026/6/30 00:47:16.251</t>
         </is>
       </c>
       <c r="C569" t="n">
@@ -59100,7 +59100,7 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>2026/6/29 23:47:21.233</t>
+          <t>2026/6/30 00:47:21.233</t>
         </is>
       </c>
       <c r="C570" t="n">
@@ -59203,7 +59203,7 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>2026/6/29 23:47:26.213</t>
+          <t>2026/6/30 00:47:26.213</t>
         </is>
       </c>
       <c r="C571" t="n">
@@ -59306,7 +59306,7 @@
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>2026/6/29 23:47:31.242</t>
+          <t>2026/6/30 00:47:31.242</t>
         </is>
       </c>
       <c r="C572" t="n">
@@ -59409,7 +59409,7 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>2026/6/29 23:47:36.249</t>
+          <t>2026/6/30 00:47:36.249</t>
         </is>
       </c>
       <c r="C573" t="n">
@@ -59512,7 +59512,7 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>2026/6/29 23:47:41.264</t>
+          <t>2026/6/30 00:47:41.264</t>
         </is>
       </c>
       <c r="C574" t="n">
@@ -59615,7 +59615,7 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>2026/6/29 23:47:46.249</t>
+          <t>2026/6/30 00:47:46.249</t>
         </is>
       </c>
       <c r="C575" t="n">
@@ -59718,7 +59718,7 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>2026/6/29 23:47:51.242</t>
+          <t>2026/6/30 00:47:51.242</t>
         </is>
       </c>
       <c r="C576" t="n">
@@ -59821,7 +59821,7 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>2026/6/29 23:47:56.261</t>
+          <t>2026/6/30 00:47:56.261</t>
         </is>
       </c>
       <c r="C577" t="n">
